--- a/docs/Marketing_Overview_Regression.xlsx
+++ b/docs/Marketing_Overview_Regression.xlsx
@@ -477,14 +477,23 @@
     <t>No layout mutation on shared dashboard</t>
   </si>
   <si>
-    <t>Reset Widgets control present but not clicked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate #reset-all-inactive-widgets
-2. Do not click on shared dashboard</t>
-  </si>
-  <si>
-    <t>Control presence documented; no reset executed</t>
+    <t>Hide Widget, Reset behavior, and hidden-widget recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Hide the Campaigns widget and confirm Hide Widget
+2. Verify Campaigns is removed from the active grid
+3. Click Reset Widgets and confirm Reset All Widgets
+4. Record whether Reset restores the hidden widget
+5. If Reset only restores positions, expand hidden widgets and drag Campaigns back
+6. Repeat for Campaigns Over Time
+7. Verify both widgets and their data are restored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each selected widget is hidden after confirmation
+Reset Widgets behavior is captured independently for each widget
+A widget not unhidden by Reset is restored from the hidden-widget panel
+Campaign cards and Campaigns Over Time bar/line graphs are healthy after recovery
+The shared dashboard is not left with hidden widgets</t>
   </si>
   <si>
     <t>REG-MO-021</t>
@@ -561,16 +570,25 @@
     <t>REG-MO-027</t>
   </si>
   <si>
-    <t>Select each campaign metric and assert graph signature updates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select each metric
-2. Compare scoped graph signatures
-3. Restore original metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active metric state updates
-Graph signature captured before/after</t>
+    <t>Every Campaigns Over Time tab has graph data and detailed tooltips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Capture the original active metric and bar/line graph signatures
+2. Select Revenue, Orders, Avg Order Value, Conversion Rate, Bounce Rate, Exit Rate, and Sessions in turn
+3. Verify the selected tab becomes active
+4. Verify both scoped bar and line graphs contain non-null data points
+5. Hover representative points on both graphs
+6. Validate tooltip details and units: currency for Revenue/AOV, percentages for rates, counts for Orders/Sessions
+7. Record any stale metric/unit tooltip behavior without skipping remaining tabs
+8. Restore the original metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All seven metric tabs exist and are selectable
+Both graphs contain live data for every data-bearing metric
+Bar and line tooltips contain campaign/time/value details
+Tooltip units correspond to the active metric
+All tabs are exercised even if one tab produces a soft live-UI finding
+Original metric is restored</t>
   </si>
   <si>
     <t>REG-MO-028</t>
@@ -625,14 +643,21 @@
     <t>REG-MO-032</t>
   </si>
   <si>
-    <t>Campaign graph context/export menu opens and dismisses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open context menu on bar graph
-2. Dismiss with Escape</t>
-  </si>
-  <si>
-    <t>Menu dismisses; no blocking overlay</t>
+    <t>Campaigns Over Time hamburger options work and restore chart state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the hamburger menu scoped to the Campaigns Over Time bar graph
+2. Verify View in Full Screen, Toggle Data Labels, and Download PNG Image options
+3. Invoke Toggle Data Labels
+4. Verify the chart remains rendered and interactive
+5. Invoke Toggle Data Labels again to restore the original state
+6. Dismiss menus and verify no overlay blocks dashboard controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected chart menu options are available
+Toggle Data Labels action is accepted and can be reversed
+Chart remains healthy after menu actions
+Menu closes without leaving a blocking overlay</t>
   </si>
   <si>
     <t>REG-MO-033</t>
@@ -655,26 +680,39 @@
     <t>Source table sort / search / clear when rows exist</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Sort Revenue
-2. Search runtime-derived source
-3. No-match then clear</t>
-  </si>
-  <si>
-    <t>Row order/search behavior validated when data present</t>
+    <t xml:space="preserve">1. If the Source table has rows, capture the visible row signature
+2. Sort Revenue; reverse direction if the first click preserves the existing order
+3. Verify visible row order changes
+4. Search using a runtime-derived source value
+5. Apply a guaranteed no-match term
+6. Clear search and restore the table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue sorting changes actual row order when multiple rows exist
+Runtime-derived search limits rows correctly
+No-match search shows a controlled empty result
+Clear restores rows
+Scenario is annotated when the Source table is absent/empty</t>
   </si>
   <si>
     <t>REG-MO-035</t>
   </si>
   <si>
-    <t>Source table page-size and export options when present</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Change page size
-2. Open Export menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page-size applies when present
-Export includes CSV/TSV/JSON/Array when present</t>
+    <t>Source table page-size, Next/Previous pagination, and export options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. If the Source table is present, change page size to a configured value
+2. If Next is enabled, capture the current row/pager signature and click Next
+3. Verify the visible page changes
+4. Click Previous and verify the original page is restored
+5. Open Export and verify CSV, TSV, JSON, and Array options when configured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page-size selection applies
+Next/Previous changes and restores visible rows when multiple pages exist
+Single-page state is handled without failure
+Configured export options are present
+Scenario is annotated when the Source table is unavailable</t>
   </si>
   <si>
     <t>REG-MO-036</t>
@@ -694,15 +732,22 @@
     <t>REG-MO-037</t>
   </si>
   <si>
-    <t>Medium table sort / search / page-size / export</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Sort Orders
-2. Change page size
-3. Open Export</t>
-  </si>
-  <si>
-    <t>Interactions succeed; export options when present</t>
+    <t>Medium table sorting, search, page-size, pagination, and export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. If the Medium table has rows, capture its visible row signature
+2. Sort Orders ascending/descending and verify row-order change
+3. Exercise runtime-derived search and clear when available
+4. Change page size
+5. Exercise enabled Next/Previous and verify page restoration
+6. Open Export and inspect configured formats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorting changes actual row order when multiple rows exist
+Search and clear preserve table usability
+Page-size and enabled pagination work
+Export options are available when configured
+Scenario is annotated when the Medium table is absent/empty</t>
   </si>
   <si>
     <t>REG-MO-038</t>
@@ -746,14 +791,23 @@
 Legend toggle restores</t>
   </si>
   <si>
-    <t>Device graph context menus dismiss without overlay block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open context menus
-2. Escape/dismiss</t>
-  </si>
-  <si>
-    <t>No blocking overlay; refresh control usable</t>
+    <t>Hamburger options work independently on different device widgets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the hamburger menu on Revenue by Device
+2. Verify chart/export options and toggle data labels on/off
+3. Open the hamburger menu on Conversion Rate by Device
+4. Invoke View in Full Screen and exit with Escape
+5. Open the hamburger menu on Sessions by Device
+6. Verify the menu is scoped to that chart and dismiss it
+7. Confirm dashboard controls remain usable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each device widget exposes its own hamburger menu
+Expected image export and chart interaction options are available
+Safe actions execute without corrupting other widgets
+Data-label/fullscreen state is restored
+No menu overlay blocks the dashboard</t>
   </si>
   <si>
     <t>REG-MO-042</t>
@@ -878,7 +932,7 @@
     <t>Profile / Site: US — GDC Test Site 2</t>
   </si>
   <si>
-    <t>Type: Regression (read-only). Do NOT Save Filter, create markers, Reset Widgets, edit/delete dashboards, or switch users.</t>
+    <t>Type: Regression. Do NOT Save Filter, create markers, edit/delete dashboards, or switch users. The controlled Hide Widget / Reset Widgets scenario must restore every hidden widget before continuing.</t>
   </si>
   <si>
     <t>Do not hard-code dashboard name, lookback, campaign names, or metric totals.</t>
@@ -896,10 +950,10 @@
     <t>Execution status: Pass</t>
   </si>
   <si>
-    <t>Execution note: Isolated run 2026-07-30: 51 passed (50 REG-MO + auth). Soft annotations: Source/Medium tables not present on live _BTT Marketing Overview layout; Event Markers may be annotated when menu mis-resolves; Tablet series data-dependent; dashboard name and lookback captured dynamically (Last 6 hours at run time).</t>
-  </si>
-  <si>
-    <t>Ambiguities: dashboard "_BTT Marketing Overview" may be site-specific; Source table may be empty; Tablet series may be empty; Viewing/Editing read-only only.</t>
+    <t>Execution note: Latest automated run: 51 passed (50 REG-MO cases plus authentication). Source/Medium tables were unavailable. Soft findings: Orders tooltip retained currency, AOV occasionally remained on Revenue, and Sessions tooltip showed percentage formatting. See allure_reports/marketing-overview-report/index.html.</t>
+  </si>
+  <si>
+    <t>Live findings: Reset Widgets may restore positions without consistently unhiding every widget; use the hidden-widget panel for recovery. Source/Medium tables may be absent. Orders/Sessions tooltip units and AOV active-state behavior are recorded as soft findings when stale.</t>
   </si>
 </sst>
 </file>

--- a/docs/Marketing_Overview_Regression.xlsx
+++ b/docs/Marketing_Overview_Regression.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="266">
-  <si>
-    <t>Marketing Overview Regression — GDC Test Site 2 (US)</t>
-  </si>
-  <si>
-    <t>Help / DOC: The Marketing Overview Page – Blue Triangle Help Center (attached PDF / Help Center)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="264">
+  <si>
+    <t>Profile: US / GDC Test Site 2 | Type: Regression (read-only) | Total TCs: 50 | Marketing Overview</t>
+  </si>
+  <si>
+    <t>tests/regression_tests/US2/business-insights/improve-traffic/marketing-overview/marketing.overview.regression.spec.ts</t>
   </si>
   <si>
     <t>Module</t>
@@ -231,9 +231,9 @@
 4. Observe breadcrumb and URL</t>
   </si>
   <si>
-    <t xml:space="preserve">Breadcrumb: Business Insights / Improve Traffic / Marketing Overview
-URL contains overview-dashboard/marketing
-No login redirect</t>
+    <t xml:space="preserve">1. Breadcrumb: Business Insights / Improve Traffic / Marketing Overview
+2. URL contains overview-dashboard/marketing
+3. No login redirect</t>
   </si>
   <si>
     <t>Pass</t>
@@ -247,9 +247,9 @@
 3. Do not assume a fixed default period (e.g. Last 6 Hours or 30 days)</t>
   </si>
   <si>
-    <t xml:space="preserve">Site is GDC Test Site 2
-Dashboard and lookback labels are non-empty live values
-Sitewide Totals and widgets render</t>
+    <t xml:space="preserve">1. Site is GDC Test Site 2
+2. Dashboard and lookback labels are non-empty live values
+3. Sitewide Totals and widgets render</t>
   </si>
   <si>
     <t>Sitewide Totals and at least one marketing widget render</t>
@@ -258,8 +258,8 @@
     <t>1. After page ready, observe Sitewide Totals and Campaigns/charts</t>
   </si>
   <si>
-    <t xml:space="preserve">Sitewide Totals visible
-At least one campaign card or Highcharts container present</t>
+    <t xml:space="preserve">1. Sitewide Totals visible
+2. At least one campaign card or Highcharts container present</t>
   </si>
   <si>
     <t>Primary widgets finish loading within bounded UI deadline</t>
@@ -268,7 +268,7 @@
     <t>1. Measure warm-session navigation until widgets ready</t>
   </si>
   <si>
-    <t>Ready within 120 seconds UI observation (not a formal backend SLA)</t>
+    <t>1. Ready within 120 seconds UI observation (not a formal backend SLA)</t>
   </si>
   <si>
     <t>REG-MO-005</t>
@@ -280,7 +280,7 @@
     <t>1. Observe document title</t>
   </si>
   <si>
-    <t>Title contains Marketing</t>
+    <t>1. Title contains Marketing</t>
   </si>
   <si>
     <t>REG-MO-006</t>
@@ -293,7 +293,7 @@
 2. Verify markers / reset / view-or-edit when configured</t>
   </si>
   <si>
-    <t>Configured controls visible or attached with accessible names/tooltips</t>
+    <t>1. Configured controls visible or attached with accessible names/tooltips</t>
   </si>
   <si>
     <t>REG-MO-007</t>
@@ -305,8 +305,8 @@
     <t>1. Enumerate #switch-dashboard options</t>
   </si>
   <si>
-    <t xml:space="preserve">No blank or duplicate option labels
-Selected dashboard non-empty</t>
+    <t xml:space="preserve">1. No blank or duplicate option labels
+2. Selected dashboard non-empty</t>
   </si>
   <si>
     <t>Manual refresh reloads widgets without duplication</t>
@@ -317,9 +317,9 @@
 3. Wait for reload</t>
   </si>
   <si>
-    <t xml:space="preserve">Widgets reload
-No duplicate graph host IDs
-Controls usable again</t>
+    <t xml:space="preserve">1. Widgets reload
+2. No duplicate graph host IDs
+3. Controls usable again</t>
   </si>
   <si>
     <t>REG-MO-009</t>
@@ -332,8 +332,8 @@
 2. Enumerate all presets</t>
   </si>
   <si>
-    <t xml:space="preserve">Presets unique and non-blank
-Record live list</t>
+    <t xml:space="preserve">1. Presets unique and non-blank
+2. Record live list</t>
   </si>
   <si>
     <t>REG-MO-010</t>
@@ -347,9 +347,9 @@
 3. Compare totals</t>
   </si>
   <si>
-    <t xml:space="preserve">Selected label changes
-Totals/widget state refreshes
-Annotate if preset missing</t>
+    <t xml:space="preserve">1. Selected label changes
+2. Totals/widget state refreshes
+3. Annotate if preset missing</t>
   </si>
   <si>
     <t>REG-MO-011</t>
@@ -362,7 +362,7 @@
 2. Compare campaign card signature</t>
   </si>
   <si>
-    <t>Widgets reload for selected period</t>
+    <t>1. Widgets reload for selected period</t>
   </si>
   <si>
     <t>REG-MO-012</t>
@@ -376,7 +376,8 @@
 3. Compare graph signature</t>
   </si>
   <si>
-    <t>Bar/line graphs refresh; do not only count containers</t>
+    <t xml:space="preserve">1. Bar/line graphs refresh
+2. do not only count containers</t>
   </si>
   <si>
     <t>REG-MO-013</t>
@@ -389,8 +390,8 @@
 2. Restore originally captured lookback</t>
   </si>
   <si>
-    <t xml:space="preserve">Period applies when available
-Original lookback restored</t>
+    <t xml:space="preserve">1. Period applies when available
+2. Original lookback restored</t>
   </si>
   <si>
     <t>REG-MO-014</t>
@@ -403,8 +404,8 @@
 2. Cancel without applying</t>
   </si>
   <si>
-    <t xml:space="preserve">Lookback remains a valid prior/selected value
-No stuck overlay</t>
+    <t xml:space="preserve">1. Lookback remains a valid prior/selected value
+2. No stuck overlay</t>
   </si>
   <si>
     <t>REG-MO-015</t>
@@ -419,9 +420,9 @@
 4. Do not wait full interval</t>
   </si>
   <si>
-    <t xml:space="preserve">Options unique
-Label updates
-Original restored</t>
+    <t xml:space="preserve">1. Options unique
+2. Label updates
+3. Original restored</t>
   </si>
   <si>
     <t>REG-MO-016</t>
@@ -435,7 +436,7 @@
 3. Confirm lookback unchanged</t>
   </si>
   <si>
-    <t>Lookback unchanged</t>
+    <t>1. Lookback unchanged</t>
   </si>
   <si>
     <t>Event Markers options sample and restore (no create/edit/delete)</t>
@@ -446,9 +447,9 @@
 3. Do not Create A New Marker</t>
   </si>
   <si>
-    <t xml:space="preserve">Options valid
-Charts update marker visibility when applicable
-Original restored</t>
+    <t xml:space="preserve">1. Options valid
+2. Charts update marker visibility when applicable
+3. Original restored</t>
   </si>
   <si>
     <t>REG-MO-018</t>
@@ -461,7 +462,7 @@
 2. Inspect drag/edit handles</t>
   </si>
   <si>
-    <t>Drag/edit handles not active in Viewing</t>
+    <t>1. Drag/edit handles not active in Viewing</t>
   </si>
   <si>
     <t>REG-MO-019</t>
@@ -474,7 +475,7 @@
 2. Return to Viewing without moving widgets</t>
   </si>
   <si>
-    <t>No layout mutation on shared dashboard</t>
+    <t>1. No layout mutation on shared dashboard</t>
   </si>
   <si>
     <t>Hide Widget, Reset behavior, and hidden-widget recovery</t>
@@ -489,11 +490,11 @@
 7. Verify both widgets and their data are restored</t>
   </si>
   <si>
-    <t xml:space="preserve">Each selected widget is hidden after confirmation
-Reset Widgets behavior is captured independently for each widget
-A widget not unhidden by Reset is restored from the hidden-widget panel
-Campaign cards and Campaigns Over Time bar/line graphs are healthy after recovery
-The shared dashboard is not left with hidden widgets</t>
+    <t xml:space="preserve">1. Each selected widget is hidden after confirmation
+2. Reset Widgets behavior is captured independently for each widget
+3. A widget not unhidden by Reset is restored from the hidden-widget panel
+4. Campaign cards and Campaigns Over Time bar/line graphs are healthy after recovery
+5. The shared dashboard is not left with hidden widgets</t>
   </si>
   <si>
     <t>REG-MO-021</t>
@@ -505,7 +506,7 @@
     <t>1. Verify title and cards #bounce-rate-card … #conversion-rate-card</t>
   </si>
   <si>
-    <t>All ten cards attached with non-empty value or controlled no-data</t>
+    <t>1. All ten cards attached with non-empty value or controlled no-data</t>
   </si>
   <si>
     <t>REG-MO-022</t>
@@ -517,7 +518,7 @@
     <t>1. Sample Bounce Rate, Revenue, Sessions, Onload formats</t>
   </si>
   <si>
-    <t>Formats match type (%, currency/count, duration) without exact values</t>
+    <t>1. Formats match type (%, currency/count, duration) without exact values</t>
   </si>
   <si>
     <t>REG-MO-023</t>
@@ -529,7 +530,7 @@
     <t>1. Hover info icons on metric cards</t>
   </si>
   <si>
-    <t>Meaningful tooltip/title text when icons present</t>
+    <t>1. Meaningful tooltip/title text when icons present</t>
   </si>
   <si>
     <t>Campaigns widget shows at least one data-bearing card</t>
@@ -539,7 +540,7 @@
 2. Validate non-empty labels/metrics</t>
   </si>
   <si>
-    <t>At least one card OR annotate controlled no-data</t>
+    <t>1. At least one card OR annotate controlled no-data</t>
   </si>
   <si>
     <t>Campaign action menu labels and safe Back navigation</t>
@@ -551,8 +552,8 @@
 4. Close extra tabs</t>
   </si>
   <si>
-    <t xml:space="preserve">Menu labels present
-Marketing Overview restores after Back</t>
+    <t xml:space="preserve">1. Menu labels present
+2. Marketing Overview restores after Back</t>
   </si>
   <si>
     <t>REG-MO-026</t>
@@ -564,7 +565,7 @@
     <t>1. Verify #revenue-campaigns … #sessions-campaigns</t>
   </si>
   <si>
-    <t>All configured metric buttons visible</t>
+    <t>1. All configured metric buttons visible</t>
   </si>
   <si>
     <t>REG-MO-027</t>
@@ -583,12 +584,12 @@
 8. Restore the original metric</t>
   </si>
   <si>
-    <t xml:space="preserve">All seven metric tabs exist and are selectable
-Both graphs contain live data for every data-bearing metric
-Bar and line tooltips contain campaign/time/value details
-Tooltip units correspond to the active metric
-All tabs are exercised even if one tab produces a soft live-UI finding
-Original metric is restored</t>
+    <t xml:space="preserve">1. All seven metric tabs exist and are selectable
+2. Both graphs contain live data for every data-bearing metric
+3. Bar and line tooltips contain campaign/time/value details
+4. Tooltip units correspond to the active metric
+5. All tabs are exercised even if one tab produces a soft live-UI finding
+6. Original metric is restored</t>
   </si>
   <si>
     <t>REG-MO-028</t>
@@ -600,7 +601,7 @@
     <t>1. Rapidly click Orders → Sessions → Revenue</t>
   </si>
   <si>
-    <t>Final active metric is Revenue</t>
+    <t>1. Final active metric is Revenue</t>
   </si>
   <si>
     <t>REG-MO-029</t>
@@ -612,7 +613,7 @@
     <t>1. Verify #top-campaigns-by-campaign-bar and -line</t>
   </si>
   <si>
-    <t>Both graphs render for data-bearing metric</t>
+    <t>1. Both graphs render for data-bearing metric</t>
   </si>
   <si>
     <t>REG-MO-030</t>
@@ -625,7 +626,7 @@
 2. Read tooltip fields</t>
   </si>
   <si>
-    <t>Tooltip content asserted when available</t>
+    <t>1. Tooltip content asserted when available</t>
   </si>
   <si>
     <t>REG-MO-031</t>
@@ -637,7 +638,7 @@
     <t>1. Toggle first legend item twice</t>
   </si>
   <si>
-    <t>Series visibility changes and restores</t>
+    <t>1. Series visibility changes and restores</t>
   </si>
   <si>
     <t>REG-MO-032</t>
@@ -654,10 +655,10 @@
 6. Dismiss menus and verify no overlay blocks dashboard controls</t>
   </si>
   <si>
-    <t xml:space="preserve">Expected chart menu options are available
-Toggle Data Labels action is accepted and can be reversed
-Chart remains healthy after menu actions
-Menu closes without leaving a blocking overlay</t>
+    <t xml:space="preserve">1. Expected chart menu options are available
+2. Toggle Data Labels action is accepted and can be reversed
+3. Chart remains healthy after menu actions
+4. Menu closes without leaving a blocking overlay</t>
   </si>
   <si>
     <t>REG-MO-033</t>
@@ -670,8 +671,8 @@
 2. Verify columns</t>
   </si>
   <si>
-    <t xml:space="preserve">Headers: Source, Revenue ($), Orders, Avg Order Value ($), Visitors, Page Views, Conversion Rate (%)
-Rows OR controlled empty annotated</t>
+    <t xml:space="preserve">1. Headers: Source, Revenue ($), Orders, Avg Order Value ($), Visitors, Page Views, Conversion Rate (%)
+2. Rows OR controlled empty annotated</t>
   </si>
   <si>
     <t>REG-MO-034</t>
@@ -688,11 +689,11 @@
 6. Clear search and restore the table</t>
   </si>
   <si>
-    <t xml:space="preserve">Revenue sorting changes actual row order when multiple rows exist
-Runtime-derived search limits rows correctly
-No-match search shows a controlled empty result
-Clear restores rows
-Scenario is annotated when the Source table is absent/empty</t>
+    <t xml:space="preserve">1. Revenue sorting changes actual row order when multiple rows exist
+2. Runtime-derived search limits rows correctly
+3. No-match search shows a controlled empty result
+4. Clear restores rows
+5. Scenario is annotated when the Source table is absent/empty</t>
   </si>
   <si>
     <t>REG-MO-035</t>
@@ -708,11 +709,11 @@
 5. Open Export and verify CSV, TSV, JSON, and Array options when configured</t>
   </si>
   <si>
-    <t xml:space="preserve">Page-size selection applies
-Next/Previous changes and restores visible rows when multiple pages exist
-Single-page state is handled without failure
-Configured export options are present
-Scenario is annotated when the Source table is unavailable</t>
+    <t xml:space="preserve">1. Page-size selection applies
+2. Next/Previous changes and restores visible rows when multiple pages exist
+3. Single-page state is handled without failure
+4. Configured export options are present
+5. Scenario is annotated when the Source table is unavailable</t>
   </si>
   <si>
     <t>REG-MO-036</t>
@@ -725,8 +726,8 @@
 2. Verify columns and sample rows</t>
   </si>
   <si>
-    <t xml:space="preserve">Stable headers present
-Formats validated without exact values</t>
+    <t xml:space="preserve">1. Stable headers present
+2. Formats validated without exact values</t>
   </si>
   <si>
     <t>REG-MO-037</t>
@@ -743,11 +744,11 @@
 6. Open Export and inspect configured formats</t>
   </si>
   <si>
-    <t xml:space="preserve">Sorting changes actual row order when multiple rows exist
-Search and clear preserve table usability
-Page-size and enabled pagination work
-Export options are available when configured
-Scenario is annotated when the Medium table is absent/empty</t>
+    <t xml:space="preserve">1. Sorting changes actual row order when multiple rows exist
+2. Search and clear preserve table usability
+3. Page-size and enabled pagination work
+4. Export options are available when configured
+5. Scenario is annotated when the Medium table is absent/empty</t>
   </si>
   <si>
     <t>REG-MO-038</t>
@@ -760,8 +761,8 @@
 2. Hover sample point</t>
   </si>
   <si>
-    <t xml:space="preserve">Graphs render
-Desktop/Mobile/Tablet series data-dependent</t>
+    <t xml:space="preserve">1. Graphs render
+2. Desktop/Mobile/Tablet series data-dependent</t>
   </si>
   <si>
     <t>REG-MO-039</t>
@@ -774,7 +775,7 @@
 2. Hover tooltip</t>
   </si>
   <si>
-    <t>Percentage presentation without exact backend values</t>
+    <t>1. Percentage presentation without exact backend values</t>
   </si>
   <si>
     <t>REG-MO-040</t>
@@ -787,8 +788,8 @@
 2. Toggle legend</t>
   </si>
   <si>
-    <t xml:space="preserve">Count-based graphs render
-Legend toggle restores</t>
+    <t xml:space="preserve">1. Count-based graphs render
+2. Legend toggle restores</t>
   </si>
   <si>
     <t>Hamburger options work independently on different device widgets</t>
@@ -803,11 +804,11 @@
 7. Confirm dashboard controls remain usable</t>
   </si>
   <si>
-    <t xml:space="preserve">Each device widget exposes its own hamburger menu
-Expected image export and chart interaction options are available
-Safe actions execute without corrupting other widgets
-Data-label/fullscreen state is restored
-No menu overlay blocks the dashboard</t>
+    <t xml:space="preserve">1. Each device widget exposes its own hamburger menu
+2. Expected image export and chart interaction options are available
+3. Safe actions execute without corrupting other widgets
+4. Data-label/fullscreen state is restored
+5. No menu overlay blocks the dashboard</t>
   </si>
   <si>
     <t>REG-MO-042</t>
@@ -821,8 +822,8 @@
 3. Cancel</t>
   </si>
   <si>
-    <t xml:space="preserve">Controls attached
-Cancel closes without applying</t>
+    <t xml:space="preserve">1. Controls attached
+2. Cancel closes without applying</t>
   </si>
   <si>
     <t>REG-MO-043</t>
@@ -836,9 +837,9 @@
 3. Clear/restore</t>
   </si>
   <si>
-    <t xml:space="preserve">Measurable refresh
-Original context restored
-Do not Save Filter</t>
+    <t xml:space="preserve">1. Measurable refresh
+2. Original context restored
+3. Do not Save Filter</t>
   </si>
   <si>
     <t>REG-MO-044</t>
@@ -852,8 +853,8 @@
 3. Restore</t>
   </si>
   <si>
-    <t xml:space="preserve">Filter applies
-Table reflects or empty state controlled</t>
+    <t xml:space="preserve">1. Filter applies
+2. Table reflects or empty state controlled</t>
   </si>
   <si>
     <t>REG-MO-045</t>
@@ -867,8 +868,8 @@
 3. Clear</t>
   </si>
   <si>
-    <t xml:space="preserve">Combination applies when options exist
-Context restored</t>
+    <t xml:space="preserve">1. Combination applies when options exist
+2. Context restored</t>
   </si>
   <si>
     <t>REG-MO-046</t>
@@ -881,7 +882,8 @@
 2. Observe Include/Exclude/Bots Only</t>
   </si>
   <si>
-    <t>Controls documented; no Save Filter</t>
+    <t xml:space="preserve">1. Controls documented
+2. no Save Filter</t>
   </si>
   <si>
     <t>Keyboard focus sample on primary controls</t>
@@ -890,7 +892,7 @@
     <t>1. Focus lookback, refresh, auto refresh, metric tab</t>
   </si>
   <si>
-    <t>Controls accept focus</t>
+    <t>1. Controls accept focus</t>
   </si>
   <si>
     <t>Responsive narrow desktop keeps essential controls reachable</t>
@@ -900,7 +902,7 @@
 2. Restore 1440</t>
   </si>
   <si>
-    <t>Lookback and Sitewide Totals remain reachable</t>
+    <t>1. Lookback and Sitewide Totals remain reachable</t>
   </si>
   <si>
     <t>Combination lookback + campaign metric + refresh without duplicates</t>
@@ -912,7 +914,7 @@
 4. Check duplicate hosts/cards</t>
   </si>
   <si>
-    <t>No duplicate graph hosts or campaignDiv IDs</t>
+    <t>1. No duplicate graph hosts or campaignDiv IDs</t>
   </si>
   <si>
     <t>Recover to original dashboard/lookback/metric context; page healthy</t>
@@ -922,8 +924,8 @@
 2. Confirm URL/title/widgets</t>
   </si>
   <si>
-    <t xml:space="preserve">Healthy Marketing Overview state
-Blocking errors annotated if any</t>
+    <t xml:space="preserve">1. Healthy Marketing Overview state
+2. Blocking errors annotated if any</t>
   </si>
   <si>
     <t>Blue Triangle Portal — Marketing Overview Regression Test Cases</t>
@@ -932,28 +934,22 @@
     <t>Profile / Site: US — GDC Test Site 2</t>
   </si>
   <si>
-    <t>Type: Regression. Do NOT Save Filter, create markers, edit/delete dashboards, or switch users. The controlled Hide Widget / Reset Widgets scenario must restore every hidden widget before continuing.</t>
-  </si>
-  <si>
-    <t>Do not hard-code dashboard name, lookback, campaign names, or metric totals.</t>
+    <t>Type: Regression (read-only). Prefer live UI; do not assert exact backend numeric values unless specified.</t>
   </si>
   <si>
     <t>Columns: Test Case ID | Type | Module | Submodule | Title | Steps | Expected Results | Status</t>
   </si>
   <si>
-    <t>Total cases: 50</t>
+    <t>Header style: bold white text on #1F4E79</t>
+  </si>
+  <si>
+    <t>Total cases: 50 (REG-MO-001 .. REG-MO-050)</t>
   </si>
   <si>
     <t>Automation: tests/regression_tests/US2/business-insights/improve-traffic/marketing-overview/marketing.overview.regression.spec.ts</t>
   </si>
   <si>
     <t>Execution status: Pass</t>
-  </si>
-  <si>
-    <t>Execution note: Latest automated run: 51 passed (50 REG-MO cases plus authentication). Source/Medium tables were unavailable. Soft findings: Orders tooltip retained currency, AOV occasionally remained on Revenue, and Sessions tooltip showed percentage formatting. See allure_reports/marketing-overview-report/index.html.</t>
-  </si>
-  <si>
-    <t>Live findings: Reset Widgets may restore positions without consistently unhiding every widget; use the hidden-widget panel for recovery. Source/Medium tables may be absent. Orders/Sessions tooltip units and AOV active-state behavior are recorded as soft findings when stale.</t>
   </si>
 </sst>
 </file>
@@ -970,7 +966,7 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="12"/>
     </font>
     <font>
       <b/>
@@ -989,7 +985,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5496"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -1018,15 +1014,17 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1369,427 +1367,424 @@
   <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="70" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-    </row>
-    <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
+    <row r="5" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>6</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="s">
+    <row r="6" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>5</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4" t="s">
+    <row r="7" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>4</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4" t="s">
+    <row r="8" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>3</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="4" t="s">
+    <row r="9" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>3</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="4" t="s">
+    <row r="10" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>3</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="4" t="s">
+    <row r="11" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>3</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="4" t="s">
+    <row r="12" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>2</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="4" t="s">
+    <row r="13" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <v>2</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="4" t="s">
+    <row r="14" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>2</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="4" t="s">
+    <row r="15" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <v>2</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="4" t="s">
+    <row r="16" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>2</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="4" t="s">
+    <row r="17" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="5">
         <v>1</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="4" t="s">
+    <row r="18" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="5">
         <v>1</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="4" t="s">
+    <row r="19" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="5">
         <v>1</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="4" t="s">
+    <row r="20" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="5">
         <v>1</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="4" t="s">
+    <row r="21" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="5">
         <v>1</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="4" t="s">
+    <row r="22" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="5">
         <v>1</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="4" t="s">
+    <row r="23" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="5">
         <v>1</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="4" t="s">
+    <row r="24" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="5">
         <v>1</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="4" t="s">
+    <row r="25" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="5">
         <v>1</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="4" t="s">
+    <row r="26" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="5">
         <v>1</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="4" t="s">
+    <row r="27" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="5">
         <v>1</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="4" t="s">
+    <row r="28" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="5">
         <v>1</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="4" t="s">
+    <row r="29" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="5">
         <v>1</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
+    <row r="30" spans="2:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="6">
         <v>50</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="6" t="s">
         <v>60</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1801,1338 +1796,1339 @@
   <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="62" customWidth="1"/>
-    <col min="6" max="7" width="68" customWidth="1"/>
+    <col min="5" max="5" width="58" customWidth="1"/>
+    <col min="6" max="6" width="68" customWidth="1"/>
+    <col min="7" max="7" width="62" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" ht="76" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="H2" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="H3" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="H4" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="B5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="H5" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="B6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="H6" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="B7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="H7" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="B8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="H8" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="B9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="H9" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="B10" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="H10" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="H11" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="H12" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="B13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="H13" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="B14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="H14" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="B15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="H15" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" ht="76" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="B16" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="H16" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="B17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="H17" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="H18" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="B19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="H19" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="B20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="H20" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" ht="124" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="B21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="H21" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="B22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="H22" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="B23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="H23" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="B24" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="H24" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="B25" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="H25" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" ht="76" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="B26" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="H26" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="4" t="s">
+      <c r="B27" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="H27" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="H27" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" ht="140" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="B28" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="H28" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="H28" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="B29" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="H29" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="H29" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="B30" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H30" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="31" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="H30" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="B31" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="H31" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="H31" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="B32" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="H32" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="H32" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" ht="108" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="B33" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="H33" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="H33" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="B34" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="H34" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="35" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="H34" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" ht="108" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="B35" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="H35" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="H35" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" ht="92" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="4" t="s">
+      <c r="B36" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="H36" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="H36" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="4" t="s">
+      <c r="B37" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="H37" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="H37" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" ht="108" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="4" t="s">
+      <c r="B38" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="H38" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="H38" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="4" t="s">
+      <c r="B39" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="H39" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="40" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="H39" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="4" t="s">
+      <c r="B40" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="H40" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+      <c r="H40" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="4" t="s">
+      <c r="B41" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="H41" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="42" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+      <c r="H41" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" ht="124" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="4" t="s">
+      <c r="B42" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="H42" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+      <c r="H42" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="4" t="s">
+      <c r="B43" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="H43" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="44" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+      <c r="H43" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="B44" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="H44" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="45" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
+      <c r="H44" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="B45" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="H45" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="46" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="H45" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="4" t="s">
+      <c r="B46" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="H46" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="47" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
+      <c r="H46" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="4" t="s">
+      <c r="B47" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="H47" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="48" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
+      <c r="H47" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="4" t="s">
+      <c r="B48" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="H48" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="49" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
+      <c r="H48" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="4" t="s">
+      <c r="B49" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="H49" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="50" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
+      <c r="H49" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" ht="76" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="4" t="s">
+      <c r="B50" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="H50" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="51" ht="100" customHeight="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
+      <c r="H50" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="4" t="s">
+      <c r="B51" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G51" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="H51" s="4" t="s">
+      <c r="H51" s="5" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3152,14 +3148,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>256</v>
       </c>
     </row>
@@ -3190,27 +3186,12 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
         <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>265</v>
       </c>
     </row>
   </sheetData>
